--- a/data/trans_camb/P05A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P05A_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-15,58</t>
+          <t>-15,12</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,18</t>
+          <t>-12,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,41</t>
+          <t>-14,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,57; 33,85</t>
+          <t>18,05; 33,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 25,28</t>
+          <t>10,32; 25,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -10,26</t>
+          <t>-20,15; -10,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,58; 36,17</t>
+          <t>20,4; 35,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,97; 38,95</t>
+          <t>23,63; 39,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -8,82</t>
+          <t>-18,71; -8,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 32,57</t>
+          <t>22,01; 33,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,3; 30,17</t>
+          <t>19,16; 30,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -11,31</t>
+          <t>-18,0; -10,45</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-83,62%</t>
+          <t>-81,12%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-78,15%</t>
+          <t>-76,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-81,11%</t>
+          <t>-79,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,56; 226,75</t>
+          <t>83,41; 223,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,96; 172,0</t>
+          <t>46,75; 175,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-92,99; -64,02</t>
+          <t>-91,07; -66,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100,57; 273,67</t>
+          <t>97,31; 267,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>112,74; 283,33</t>
+          <t>109,55; 304,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,69; -60,29</t>
+          <t>-87,5; -61,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>106,89; 213,56</t>
+          <t>103,9; 215,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,74; 197,02</t>
+          <t>95,91; 194,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,16; -69,44</t>
+          <t>-86,2; -68,86</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,38</t>
+          <t>-18,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-20,54</t>
+          <t>-20,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 12,16</t>
+          <t>-0,78; 12,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 27,59</t>
+          <t>15,62; 27,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,58; -11,6</t>
+          <t>-23,71; -11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 11,8</t>
+          <t>0,43; 11,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 22,32</t>
+          <t>9,8; 22,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,58; -17,37</t>
+          <t>-27,47; -17,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 10,42</t>
+          <t>1,31; 10,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,88</t>
+          <t>13,39; 22,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,39; -16,34</t>
+          <t>-24,71; -16,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-55,76%</t>
+          <t>-56,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-59,5%</t>
+          <t>-59,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 40,51</t>
+          <t>-1,65; 41,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,75; 94,19</t>
+          <t>42,46; 95,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,68; -38,6</t>
+          <t>-67,23; -39,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 34,87</t>
+          <t>1,11; 35,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,62; 68,27</t>
+          <t>25,51; 67,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,1; -53,58</t>
+          <t>-70,91; -53,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 31,94</t>
+          <t>3,65; 32,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,99; 71,12</t>
+          <t>36,16; 70,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,81; -49,89</t>
+          <t>-67,06; -50,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,25</t>
+          <t>-16,96</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,86</t>
+          <t>-7,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,29; 30,51</t>
+          <t>15,51; 30,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,04</t>
+          <t>1,92; 15,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 8,38</t>
+          <t>-4,4; 8,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 22,02</t>
+          <t>6,08; 21,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -3,36</t>
+          <t>-17,62; -3,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,35; -10,17</t>
+          <t>-23,4; -10,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 24,61</t>
+          <t>13,54; 23,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,5</t>
+          <t>-5,65; 4,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,73</t>
+          <t>-12,31; -3,44</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,48%</t>
+          <t>-43,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-25,81%</t>
+          <t>-25,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,8; 168,18</t>
+          <t>60,23; 173,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,51; 88,43</t>
+          <t>6,84; 89,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 46,62</t>
+          <t>-17,41; 46,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,51; 63,03</t>
+          <t>14,52; 59,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -9,47</t>
+          <t>-42,11; -8,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,25; -29,73</t>
+          <t>-55,24; -31,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,76; 89,7</t>
+          <t>40,55; 85,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 16,08</t>
+          <t>-17,33; 15,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,05; -10,1</t>
+          <t>-36,72; -12,08</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,77</t>
+          <t>-10,49</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,14</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,84</t>
+          <t>-6,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 10,57</t>
+          <t>-3,33; 10,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,79</t>
+          <t>-5,59; 8,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -1,56</t>
+          <t>-17,43; -4,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 23,15</t>
+          <t>9,88; 22,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 18,31</t>
+          <t>4,25; 18,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -1,78</t>
+          <t>-8,95; 2,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,85</t>
+          <t>5,13; 14,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,66</t>
+          <t>1,56; 11,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -3,91</t>
+          <t>-11,34; -1,94</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,76%</t>
+          <t>-35,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,03%</t>
+          <t>-14,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-32,74%</t>
+          <t>-25,6%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 40,96</t>
+          <t>-9,76; 40,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 29,96</t>
+          <t>-16,75; 32,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,07; -5,41</t>
+          <t>-53,47; -14,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,22; 110,71</t>
+          <t>36,4; 108,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,47; 85,2</t>
+          <t>16,23; 85,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -7,88</t>
+          <t>-32,49; 12,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,73; 61,24</t>
+          <t>17,15; 59,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,04; 47,37</t>
+          <t>5,28; 44,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,04; -15,34</t>
+          <t>-38,62; -7,91</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-42,29</t>
+          <t>-41,15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-42,58</t>
+          <t>-41,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,14; 31,32</t>
+          <t>12,12; 32,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,95; -15,04</t>
+          <t>-32,09; -14,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-49,71; -35,39</t>
+          <t>-48,97; -33,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,31; 27,75</t>
+          <t>7,77; 27,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,44; -10,88</t>
+          <t>-29,52; -10,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-49,27; -35,45</t>
+          <t>-49,15; -35,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,29; 26,61</t>
+          <t>13,0; 27,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -15,29</t>
+          <t>-28,91; -16,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-47,65; -37,1</t>
+          <t>-46,98; -36,86</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-89,93%</t>
+          <t>-87,51%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-93,15%</t>
+          <t>-91,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,44; 74,83</t>
+          <t>23,02; 77,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,89; -34,77</t>
+          <t>-63,46; -34,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,5; -82,41</t>
+          <t>-93,19; -78,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,07; 72,64</t>
+          <t>15,77; 71,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -28,4</t>
+          <t>-59,84; -27,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-98,31; -90,03</t>
+          <t>-97,68; -91,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,2; 63,48</t>
+          <t>25,61; 63,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-57,4; -36,35</t>
+          <t>-58,2; -37,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-96,21; -89,14</t>
+          <t>-94,46; -86,96</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-7,69</t>
+          <t>-7,48</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>26,41; 41,78</t>
+          <t>26,91; 41,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15,84; 30,89</t>
+          <t>14,96; 30,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 8,67</t>
+          <t>-4,07; 8,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,59; 23,09</t>
+          <t>7,74; 22,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 11,87</t>
+          <t>-3,81; 12,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -1,22</t>
+          <t>-13,64; -0,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,02; 30,17</t>
+          <t>18,9; 29,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,16; 18,9</t>
+          <t>8,01; 18,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 1,66</t>
+          <t>-7,39; 1,64</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-27,11%</t>
+          <t>-26,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-11,96%</t>
+          <t>-12,63%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>125,5; 303,6</t>
+          <t>129,83; 315,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>80,61; 234,27</t>
+          <t>74,8; 229,26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 62,37</t>
+          <t>-20,07; 61,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23,44; 94,13</t>
+          <t>23,71; 92,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 48,46</t>
+          <t>-12,37; 51,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-44,45; -4,86</t>
+          <t>-42,64; -3,69</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,82; 151,65</t>
+          <t>75,24; 151,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28,58; 94,35</t>
+          <t>32,66; 94,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 8,73</t>
+          <t>-29,85; 8,1</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,46</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>5,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>13,14; 23,63</t>
+          <t>13,11; 24,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,22</t>
+          <t>9,72; 20,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,09</t>
+          <t>3,37; 14,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,29</t>
+          <t>1,39; 12,36</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,87; 12,58</t>
+          <t>2,27; 13,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,43; 43,14</t>
+          <t>-3,1; 6,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,9; 16,24</t>
+          <t>8,64; 16,49</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7,81; 15,57</t>
+          <t>7,17; 15,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,96; 37,08</t>
+          <t>1,73; 8,71</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>49,34; 110,54</t>
+          <t>50,44; 115,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>38,15; 94,89</t>
+          <t>38,17; 97,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12,47; 68,52</t>
+          <t>12,74; 66,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,44; 40,05</t>
+          <t>3,77; 40,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,12; 41,39</t>
+          <t>5,9; 43,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,19; 139,47</t>
+          <t>-8,43; 23,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,99; 61,53</t>
+          <t>28,31; 62,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>25,21; 58,44</t>
+          <t>23,11; 56,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16,99; 128,94</t>
+          <t>5,04; 32,45</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-28,03</t>
+          <t>-23,47</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-22,14</t>
+          <t>-21,07</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-25,71</t>
+          <t>-22,25</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -9,86</t>
+          <t>-19,14; -9,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -6,53</t>
+          <t>-15,86; -6,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -22,3</t>
+          <t>-28,23; -18,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-23,89; -14,52</t>
+          <t>-23,97; -14,71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-19,67; -10,21</t>
+          <t>-19,83; -10,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -17,77</t>
+          <t>-25,68; -16,67</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -13,22</t>
+          <t>-20,01; -13,17</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -9,85</t>
+          <t>-16,61; -9,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-32,08; -21,71</t>
+          <t>-25,82; -19,04</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-71,19%</t>
+          <t>-59,61%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-52,01%</t>
+          <t>-49,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-62,69%</t>
+          <t>-54,27%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-46,53; -26,57</t>
+          <t>-45,53; -25,15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-38,65; -17,28</t>
+          <t>-38,34; -18,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,56; -58,13</t>
+          <t>-67,55; -51,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -35,72</t>
+          <t>-53,12; -36,56</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-43,94; -25,91</t>
+          <t>-43,82; -24,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-59,21; -43,92</t>
+          <t>-56,68; -41,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-47,23; -33,88</t>
+          <t>-46,98; -33,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,12; -25,11</t>
+          <t>-38,46; -25,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-76,27; -54,24</t>
+          <t>-59,71; -48,24</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-10,97</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-10,83</t>
+          <t>-14,03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-11,51</t>
+          <t>-12,51</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,28</t>
+          <t>7,9; 12,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,6</t>
+          <t>4,22; 8,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -9,92</t>
+          <t>-13,09; -8,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,61</t>
+          <t>3,05; 7,64</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,41</t>
+          <t>0,02; 4,7</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 4,42</t>
+          <t>-16,05; -11,9</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,44</t>
+          <t>6,15; 9,57</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,79</t>
+          <t>2,57; 5,91</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -2,81</t>
+          <t>-13,91; -11,09</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-41,79%</t>
+          <t>-37,16%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-31,46%</t>
+          <t>-40,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-35,96%</t>
+          <t>-39,09%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>25,96; 43,73</t>
+          <t>26,31; 43,88</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>13,43; 30,16</t>
+          <t>13,65; 30,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -34,47</t>
+          <t>-43,31; -31,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,2; 22,51</t>
+          <t>8,59; 23,08</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 13,2</t>
+          <t>0,11; 14,36</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 13,33</t>
+          <t>-45,13; -36,02</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,72; 29,92</t>
+          <t>18,77; 30,56</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,54</t>
+          <t>7,74; 18,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-45,53; -8,88</t>
+          <t>-42,38; -35,29</t>
         </is>
       </c>
     </row>
